--- a/dcf/NET.xlsx
+++ b/dcf/NET.xlsx
@@ -361,77 +361,77 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 15.1x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -867,7 +867,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1122,184 +1122,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>12.1</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>32.68761448112445</v>
+        <v>40.1958310293425</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>31.56916505531531</v>
+        <v>38.74488669598174</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>30.503545507642</v>
+        <v>37.36289727228801</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>29.48801852816929</v>
+        <v>36.04627609593339</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>28.52000059880275</v>
+        <v>34.7916385499529</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>27.59705269958007</v>
+        <v>33.59578982966212</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>26.71687161527833</v>
+        <v>32.45571350089852</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>13.1</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>35.1096198192593</v>
+        <v>42.61783636747736</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>33.88391397165932</v>
+        <v>41.05963561232574</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>32.71623962526974</v>
+        <v>39.57559138991576</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>31.60358548551255</v>
+        <v>38.16184305327664</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>30.5431096153028</v>
+        <v>36.81474756645296</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>29.53212919315493</v>
+        <v>35.53086632323697</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>28.56811093322032</v>
+        <v>34.30695281884051</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>14.1</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>37.53162515739416</v>
+        <v>45.03984170561221</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>36.19866288800333</v>
+        <v>43.37438452866976</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>34.92893374289748</v>
+        <v>41.78828550754351</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>33.7191524428558</v>
+        <v>40.2774100106199</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>32.56621863180285</v>
+        <v>38.837856582953</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>31.46720568672978</v>
+        <v>37.46594281681184</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>30.41935025116232</v>
+        <v>36.1581921367825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>39.95363049552902</v>
+        <v>47.46184704374707</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>38.51341180434734</v>
+        <v>45.68913344501376</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>37.14162786052524</v>
+        <v>44.00097962517125</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>35.83471940019906</v>
+        <v>42.39297696796316</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>34.58932764830291</v>
+        <v>40.86096559945306</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>33.40228218030464</v>
+        <v>39.40101931038669</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>32.27058956910432</v>
+        <v>38.00943145472451</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>42.37563583366388</v>
+        <v>49.88385238188194</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>40.82816072069135</v>
+        <v>48.00388236135778</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>39.35432197815299</v>
+        <v>46.21367374279901</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>37.95028635754232</v>
+        <v>44.50854392530643</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>36.61243666480295</v>
+        <v>42.88407461595312</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>35.33735867387949</v>
+        <v>41.33609580396155</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>34.12182888704631</v>
+        <v>39.86067077266651</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>17.1</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>44.79764117179872</v>
+        <v>52.30585772001678</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>43.14290963703536</v>
+        <v>50.31863127770178</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>41.56701609578073</v>
+        <v>48.42636786042676</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>40.06585331488558</v>
+        <v>46.62411088264967</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>38.63554568130301</v>
+        <v>44.90718363245317</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>37.27243516745435</v>
+        <v>43.2711722975364</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>35.97306820498831</v>
+        <v>41.71191009060849</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>18.1</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>47.21964650993359</v>
+        <v>54.72786305815165</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>45.45765855337937</v>
+        <v>52.63338019404579</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>43.77971021340848</v>
+        <v>50.63906197805451</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>42.18142027222884</v>
+        <v>48.73967783999294</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>40.65865469780306</v>
+        <v>46.93029264895321</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>39.2075116610292</v>
+        <v>45.20624879111126</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>37.8243075229303</v>
+        <v>43.5631494085505</v>
       </c>
     </row>
     <row r="13">
@@ -1322,7 +1322,7 @@
         <v>0.1163855786089606</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7331755883455519</v>
+        <v>0.7237212883645788</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24369,7 +24369,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="46">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>35.83471940019906</v>
+        <v>42.39297696796316</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>50.28619052581541</v>
+        <v>58.65535438459749</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>25.19121526017965</v>
+        <v>30.28403274986492</v>
       </c>
     </row>
     <row r="59">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24806,7 +24806,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24825,7 +24829,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24833,7 +24837,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24852,7 +24860,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24860,7 +24868,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24879,7 +24891,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24887,7 +24899,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24906,7 +24922,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24914,7 +24930,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24933,7 +24953,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24941,7 +24961,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24960,7 +24984,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24968,7 +24992,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24987,7 +25015,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24995,7 +25023,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25014,7 +25046,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25022,7 +25054,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25041,7 +25077,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25049,7 +25085,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25068,7 +25108,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25076,7 +25116,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25095,7 +25139,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25103,7 +25147,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25122,12 +25170,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.1x</t>
         </is>
       </c>
       <c r="F20" s="31" t="inlineStr"/>
@@ -25149,7 +25197,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25157,7 +25205,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25176,7 +25228,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/dcf/NET.xlsx
+++ b/dcf/NET.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.1013855786089606</v>
+        <v>0.1015642689890366</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.1063855786089606</v>
+        <v>0.1065642689890366</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.1113855786089606</v>
+        <v>0.1115642689890366</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1163855786089606</v>
+        <v>0.1165642689890366</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1213855786089606</v>
+        <v>0.1215642689890366</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1263855786089606</v>
+        <v>0.1265642689890366</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1313855786089606</v>
+        <v>0.1315642689890366</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>12.1</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>40.1958310293425</v>
+        <v>32.55106216714969</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>38.74488669598174</v>
+        <v>31.43104215234225</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>37.36289727228801</v>
+        <v>30.36414307891505</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>36.04627609593339</v>
+        <v>29.34760502827685</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>34.7916385499529</v>
+        <v>28.37882344198668</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>33.59578982966212</v>
+        <v>27.45533972008499</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>32.45571350089852</v>
+        <v>26.57483242735688</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>13.1</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>42.61783636747736</v>
+        <v>34.41204368744383</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>41.05963561232574</v>
+        <v>33.20962474624221</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>39.57559138991576</v>
+        <v>32.0643222241739</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>38.16184305327664</v>
+        <v>30.97316578219509</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>36.81474756645296</v>
+        <v>29.93335239398087</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>35.53086632323697</v>
+        <v>28.94223621627621</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>34.30695281884051</v>
+        <v>27.99731911447782</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>14.1</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>45.03984170561221</v>
+        <v>36.27302520773797</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>43.37438452866976</v>
+        <v>34.98820734014216</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>41.78828550754351</v>
+        <v>33.76450136943275</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>40.2774100106199</v>
+        <v>32.59872653611333</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>38.837856582953</v>
+        <v>31.48788134597505</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>37.46594281681184</v>
+        <v>30.42913271246744</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>36.1581921367825</v>
+        <v>29.41980580159876</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>15.1</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>47.46184704374707</v>
+        <v>38.1340067280321</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>45.68913344501376</v>
+        <v>36.76678993404212</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>44.00097962517125</v>
+        <v>35.4646805146916</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>42.39297696796316</v>
+        <v>34.22428729003157</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>40.86096559945306</v>
+        <v>33.04241029796923</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>39.40101931038669</v>
+        <v>31.91602920865866</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>38.00943145472451</v>
+        <v>30.8422924887197</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>16.1</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>49.88385238188194</v>
+        <v>39.99498824832624</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>48.00388236135778</v>
+        <v>38.54537252794208</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>46.21367374279901</v>
+        <v>37.16485965995046</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>44.50854392530643</v>
+        <v>35.84984804394981</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>42.88407461595312</v>
+        <v>34.59693924996343</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>41.33609580396155</v>
+        <v>33.40292570484989</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>39.86067077266651</v>
+        <v>32.26477917584064</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>17.1</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>52.30585772001678</v>
+        <v>41.85596976862038</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>50.31863127770178</v>
+        <v>40.32395512184203</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>48.42636786042676</v>
+        <v>38.86503880520931</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>46.62411088264967</v>
+        <v>37.47540879786805</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>44.90718363245317</v>
+        <v>36.15146820195761</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>43.2711722975364</v>
+        <v>34.88982220104112</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>41.71191009060849</v>
+        <v>33.68726586296158</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>18.1</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>54.72786305815165</v>
+        <v>43.71695128891452</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>52.63338019404579</v>
+        <v>42.10253771574198</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>50.63906197805451</v>
+        <v>40.56521795046816</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>48.73967783999294</v>
+        <v>39.10096955178629</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>46.93029264895321</v>
+        <v>37.70599715395179</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>45.20624879111126</v>
+        <v>36.37671869723234</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>43.5631494085505</v>
+        <v>35.10975255008252</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>242.4100036621094</v>
+        <v>268.1650085449219</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1163855786089606</v>
+        <v>0.1165642689890366</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>15.1</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7237212883645788</v>
+        <v>0.7347074395937582</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>242.4100036621094</v>
+        <v>268.1650085449219</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>42.39297696796316</v>
+        <v>34.22428729003157</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>58.65535438459749</v>
+        <v>46.02213478617704</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>30.28403274986492</v>
+        <v>25.20655665174684</v>
       </c>
     </row>
     <row r="59">
